--- a/Excel/ShengxiaoCopyConfig.xlsx
+++ b/Excel/ShengxiaoCopyConfig.xlsx
@@ -30,23 +30,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>MapName</t>
   </si>
   <si>
-    <t>ItemType</t>
-  </si>
-  <si>
-    <t>ItemIdList</t>
-  </si>
-  <si>
-    <t>ItemQuantity</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -56,37 +50,28 @@
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>天级副本</t>
-  </si>
-  <si>
-    <t>5,9,5,9,15,4</t>
-  </si>
-  <si>
-    <t>4111,4003,4004,4013,4014,36</t>
-  </si>
-  <si>
-    <t>10000,100,10,10,50,2</t>
-  </si>
-  <si>
-    <t>地级副本</t>
-  </si>
-  <si>
-    <t>11000,110,11,11,55,2</t>
-  </si>
-  <si>
-    <t>玄级副本</t>
-  </si>
-  <si>
-    <t>12000,120,12,12,60,2</t>
-  </si>
-  <si>
-    <t>黄级副本</t>
-  </si>
-  <si>
-    <t>13000,130,13,13,65,2</t>
+    <t>生肖·天级副本</t>
+  </si>
+  <si>
+    <t>生肖·地级副本</t>
+  </si>
+  <si>
+    <t>生肖·玄级副本</t>
+  </si>
+  <si>
+    <t>生肖·黄级副本</t>
+  </si>
+  <si>
+    <t>星座·宇级副本</t>
+  </si>
+  <si>
+    <t>星座·宙级副本</t>
+  </si>
+  <si>
+    <t>星座·洪级副本</t>
+  </si>
+  <si>
+    <t>星座·荒级副本</t>
   </si>
 </sst>
 </file>
@@ -726,20 +711,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1059,247 +1038,188 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6666666666667" style="3" customWidth="1"/>
-    <col min="7" max="7" width="21.9166666666667" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="13.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:7">
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:5">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:7">
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:5">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:7">
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:5">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:7">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:5">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:5">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7" t="s">
+    </row>
+    <row r="11" customHeight="1" spans="1:5">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="5:6">
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" customHeight="1" spans="5:6">
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="5:6">
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" customHeight="1" spans="5:6">
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" customHeight="1" spans="5:6">
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" customHeight="1" spans="5:6">
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" customHeight="1" spans="5:6">
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="5:6">
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="5:6">
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="5:6">
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="5:6">
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" customHeight="1" spans="5:6">
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" customHeight="1" spans="5:6">
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="5:6">
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="5:6">
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" customHeight="1" spans="6:6">
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="6:6">
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" customHeight="1" spans="6:6">
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="6:6">
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" customHeight="1" spans="6:6">
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="6:6">
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="6:6">
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="6:6">
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="6:6">
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="6:6">
-      <c r="F34" s="1"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:5">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:5">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:5">
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:5">
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:5">
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" customHeight="1" spans="4:4">
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" customHeight="1" spans="4:4">
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" customHeight="1" spans="4:4">
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" customHeight="1" spans="4:4">
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" customHeight="1" spans="4:4">
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" customHeight="1" spans="4:4">
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" customHeight="1" spans="4:4">
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" customHeight="1" spans="4:4">
+      <c r="D24" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 E3:E5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ShengxiaoCopyConfig.xlsx
+++ b/Excel/ShengxiaoCopyConfig.xlsx
@@ -30,12 +30,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>Step</t>
   </si>
   <si>
     <t>MapName</t>
@@ -1038,26 +1041,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="13.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1069,12 +1072,15 @@
       <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1082,144 +1088,185 @@
       <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:5">
+      <c r="F5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:6">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:5">
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:6">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:5">
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:6">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:5">
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:6">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:5">
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:6">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
         <v>2</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:5">
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:6">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:5">
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:6">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:5">
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:6">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:5">
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:6">
       <c r="D14" s="4"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:5">
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:6">
       <c r="D15" s="4"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:5">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:6">
       <c r="D16" s="4"/>
-    </row>
-    <row r="17" customHeight="1" spans="4:4">
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" customHeight="1" spans="4:5">
       <c r="D17" s="4"/>
-    </row>
-    <row r="18" customHeight="1" spans="4:4">
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" customHeight="1" spans="4:5">
       <c r="D18" s="4"/>
-    </row>
-    <row r="19" customHeight="1" spans="4:4">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" customHeight="1" spans="4:5">
       <c r="D19" s="4"/>
-    </row>
-    <row r="20" customHeight="1" spans="4:4">
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" customHeight="1" spans="4:5">
       <c r="D20" s="4"/>
-    </row>
-    <row r="21" customHeight="1" spans="4:4">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" customHeight="1" spans="4:5">
       <c r="D21" s="4"/>
-    </row>
-    <row r="22" customHeight="1" spans="4:4">
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" customHeight="1" spans="4:5">
       <c r="D22" s="4"/>
-    </row>
-    <row r="23" customHeight="1" spans="4:4">
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" customHeight="1" spans="4:5">
       <c r="D23" s="4"/>
-    </row>
-    <row r="24" customHeight="1" spans="4:4">
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" customHeight="1" spans="4:5">
       <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 E3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 F3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ShengxiaoCopyConfig.xlsx
+++ b/Excel/ShengxiaoCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -65,16 +65,28 @@
     <t>生肖·黄级副本</t>
   </si>
   <si>
-    <t>星座·宇级副本</t>
-  </si>
-  <si>
-    <t>星座·宙级副本</t>
-  </si>
-  <si>
-    <t>星座·洪级副本</t>
-  </si>
-  <si>
-    <t>星座·荒级副本</t>
+    <t>星座·天级副本</t>
+  </si>
+  <si>
+    <t>星座·地级副本</t>
+  </si>
+  <si>
+    <t>星座·玄级副本</t>
+  </si>
+  <si>
+    <t>星座·黄级副本</t>
+  </si>
+  <si>
+    <t>命宫·天级副本</t>
+  </si>
+  <si>
+    <t>命宫·地级副本</t>
+  </si>
+  <si>
+    <t>命宫·玄级副本</t>
+  </si>
+  <si>
+    <t>命宫·黄级副本</t>
   </si>
 </sst>
 </file>
@@ -1221,46 +1233,86 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:6">
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="1:6">
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="16" customHeight="1" spans="1:6">
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" customHeight="1" spans="4:5">
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" customHeight="1" spans="4:5">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:6">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:6">
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" customHeight="1" spans="4:5">
+    <row r="19" customHeight="1" spans="3:6">
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" customHeight="1" spans="4:5">
+    <row r="20" customHeight="1" spans="3:6">
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" customHeight="1" spans="4:5">
+    <row r="21" customHeight="1" spans="3:6">
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" customHeight="1" spans="4:5">
+    <row r="22" customHeight="1" spans="3:6">
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" customHeight="1" spans="4:5">
+    <row r="23" customHeight="1" spans="3:6">
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" customHeight="1" spans="4:5">
+    <row r="24" customHeight="1" spans="3:6">
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
